--- a/challenge 2026 12.xlsx
+++ b/challenge 2026 12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjakob\Downloads\feltölteni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8CA73EA-380B-4365-B38A-1095AA5CE173}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FCA219-966C-4A0E-ABCD-89FD33279853}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="Éves diagram" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1009,22 +1008,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -1048,13 +1031,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Éves diagram-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="Éves diagram-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1119,7 +1118,7 @@
           <c:order val="0"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="4285F4"/>
             </a:solidFill>
             <a:ln cmpd="sng">
               <a:solidFill>
@@ -1477,7 +1476,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008E6A3848}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1555,7 +1554,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000E7A3634F}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1592,7 +1591,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000FF44816C}"/>
             </a:ext>
             <a:ext uri="GoogleSheetsCustomDataVersion1">
-              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" pictureOfChart="1"/>
+              <go:sheetsCustomData xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1854,7 +1853,7 @@
     <col min="2" max="2" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:27">
+    <row r="3" spans="2:27" ht="12.75">
       <c r="B3" s="1"/>
       <c r="C3" s="2">
         <v>46042</v>
@@ -3050,9 +3049,27 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="23" spans="2:27">
+    <row r="23" spans="2:27" ht="12.75">
       <c r="B23" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="C23" s="9">
+        <v>66.5</v>
+      </c>
+      <c r="D23" s="9">
+        <v>66.5</v>
+      </c>
+      <c r="E23" s="9">
+        <v>66.5</v>
+      </c>
+      <c r="F23" s="9">
+        <v>66.5</v>
+      </c>
+      <c r="G23" s="9">
+        <v>66.5</v>
+      </c>
+      <c r="H23" s="9">
+        <v>66.5</v>
       </c>
       <c r="I23" s="9">
         <v>66.5</v>
